--- a/data/trans_orig/IP07C07-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07C07-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2007 (tasa de respuesta: 88,89%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a en 2007 (tasa de respuesta: 88,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3984</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10978</t>
+          <t>11458</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12532</t>
+          <t>12323</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>9042</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21164</t>
+          <t>20023</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14131</t>
+          <t>14406</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12144</t>
+          <t>12358</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>11797</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23238</t>
+          <t>23627</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17018</t>
+          <t>16731</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27067</t>
+          <t>26525</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13370</t>
+          <t>13495</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22727</t>
+          <t>22945</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32629</t>
+          <t>33183</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46462</t>
+          <t>46635</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,81%</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2292</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8488</t>
+          <t>8700</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>9796</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6916</t>
+          <t>6827</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16537</t>
+          <t>15706</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>29,42%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2835</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9627</t>
+          <t>9253</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10236</t>
+          <t>9749</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>6900</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16376</t>
+          <t>16986</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10217</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17883</t>
+          <t>18321</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12069</t>
+          <t>12424</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20986</t>
+          <t>20413</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25035</t>
+          <t>25067</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36530</t>
+          <t>36365</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,12%</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9031</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5975</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15003</t>
+          <t>14950</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9704</t>
+          <t>9989</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>21369</t>
+          <t>21175</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1565</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7707</t>
+          <t>8178</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13936</t>
+          <t>13783</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8145</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18998</t>
+          <t>19551</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14505</t>
+          <t>14959</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22869</t>
+          <t>23281</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25739</t>
+          <t>25963</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36647</t>
+          <t>36753</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>42893</t>
+          <t>43186</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>57119</t>
+          <t>57770</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>72,11%</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>3412</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1836</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>8714</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10190</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10585</t>
+          <t>9979</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22273</t>
+          <t>21242</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12392</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23908</t>
+          <t>24082</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25374</t>
+          <t>25188</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>41273</t>
+          <t>41510</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14940</t>
+          <t>15461</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27910</t>
+          <t>28086</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11889</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>23998</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29731</t>
+          <t>30753</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>47155</t>
+          <t>48454</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>35877</t>
+          <t>36876</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>50999</t>
+          <t>52016</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>37280</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51804</t>
+          <t>51725</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>77480</t>
+          <t>78237</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>99452</t>
+          <t>98807</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,22%</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>697</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7335</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>612</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5570</t>
+          <t>5820</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13783</t>
+          <t>14349</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18216</t>
+          <t>18358</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15586</t>
+          <t>16372</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>29332</t>
+          <t>28863</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>17856</t>
+          <t>17839</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>8325</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>19372</t>
+          <t>18679</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>19284</t>
+          <t>19572</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>33933</t>
+          <t>33889</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,13%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>18150</t>
+          <t>18441</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>29314</t>
+          <t>29249</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>25152</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>37485</t>
+          <t>37736</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>47280</t>
+          <t>47333</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>64367</t>
+          <t>63846</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>58,65%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10815</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7387</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6134</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>16150</t>
+          <t>15595</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14691</t>
+          <t>15246</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>12443</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>12547</t>
+          <t>12529</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>24563</t>
+          <t>24969</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,46%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>15936</t>
+          <t>15458</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>25550</t>
+          <t>25842</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>14593</t>
+          <t>14832</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>23588</t>
+          <t>23288</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>33335</t>
+          <t>32600</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>46889</t>
+          <t>46126</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>67,36%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>627</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>5576</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>7301</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>10028</t>
+          <t>10090</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>12494</t>
+          <t>13392</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>8672</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>6773</t>
+          <t>6797</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>17684</t>
+          <t>17735</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>37963</t>
+          <t>39377</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>59412</t>
+          <t>58728</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>47843</t>
+          <t>46074</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>70001</t>
+          <t>68382</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>91165</t>
+          <t>91030</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>121270</t>
+          <t>120708</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,87%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>52684</t>
+          <t>50918</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>73528</t>
+          <t>74081</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>49793</t>
+          <t>49334</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>72029</t>
+          <t>72710</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,47 +5213,47 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
+          <t>25,22%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>123268</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>106693</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>137910</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>22,33%</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>19,33%</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
           <t>24,99%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>123268</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>108043</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>140590</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>22,33%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>19,58%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>25,47%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>130655</t>
+          <t>129053</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>156843</t>
+          <t>154925</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>147621</t>
+          <t>148643</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>175955</t>
+          <t>176605</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>287289</t>
+          <t>288041</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>324916</t>
+          <t>324422</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,78%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2012 (tasa de respuesta: 95,1%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a en 2012 (tasa de respuesta: 95,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>574</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>666</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5043</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13314</t>
+          <t>13105</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>8361</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17540</t>
+          <t>17770</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15167</t>
+          <t>15152</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27121</t>
+          <t>27274</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,34%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6791</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15753</t>
+          <t>16221</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>3894</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12871</t>
+          <t>12630</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25272</t>
+          <t>24765</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>34,82%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11368</t>
+          <t>11180</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21113</t>
+          <t>21154</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8533</t>
+          <t>8115</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17808</t>
+          <t>16866</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22232</t>
+          <t>22450</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35186</t>
+          <t>36275</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>51,0%</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5686</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>600</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>4897</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13690</t>
+          <t>13970</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17877</t>
+          <t>16792</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>8371</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17617</t>
+          <t>17218</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>6785</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10450</t>
+          <t>10621</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21473</t>
+          <t>22285</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>33,62%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9825</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19028</t>
+          <t>19214</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16128</t>
+          <t>16062</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25678</t>
+          <t>25344</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28817</t>
+          <t>28883</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42003</t>
+          <t>41789</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,05%</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>3800</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>632</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5473</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5255</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13965</t>
+          <t>13993</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11292</t>
+          <t>11134</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22812</t>
+          <t>22091</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>29,96%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>6335</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15064</t>
+          <t>15765</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5188</t>
+          <t>5394</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13024</t>
+          <t>13235</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13885</t>
+          <t>13466</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25833</t>
+          <t>26485</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,92%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17141</t>
+          <t>16974</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27848</t>
+          <t>27210</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9867</t>
+          <t>9707</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18298</t>
+          <t>18364</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>28943</t>
+          <t>28710</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>42961</t>
+          <t>42857</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>58,13%</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3670</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>609</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9107</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11797</t>
+          <t>11832</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12785</t>
+          <t>12928</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25630</t>
+          <t>25655</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21575</t>
+          <t>21313</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>37196</t>
+          <t>36241</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>38027</t>
+          <t>38898</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>57284</t>
+          <t>58694</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>32,2%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8993</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20435</t>
+          <t>20863</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5793</t>
+          <t>5991</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15484</t>
+          <t>15558</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16999</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31978</t>
+          <t>32237</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41603</t>
+          <t>41043</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>55867</t>
+          <t>55637</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>45140</t>
+          <t>45006</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>62644</t>
+          <t>62108</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>92132</t>
+          <t>91295</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>113286</t>
+          <t>112928</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,94%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>657</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7035</t>
+          <t>7893</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8781</t>
+          <t>9274</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>617</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>6236</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7560</t>
+          <t>7737</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3096</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11222</t>
+          <t>11229</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>13156</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>24794</t>
+          <t>24518</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8459</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>19444</t>
+          <t>19480</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>23853</t>
+          <t>23233</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>40815</t>
+          <t>40308</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>11305</t>
+          <t>10631</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>22601</t>
+          <t>22821</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>9828</t>
+          <t>9779</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>21047</t>
+          <t>21222</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>23627</t>
+          <t>23528</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>38787</t>
+          <t>39905</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>27,45%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>28290</t>
+          <t>28363</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>41976</t>
+          <t>42091</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>31044</t>
+          <t>30687</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>44662</t>
+          <t>44724</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>63669</t>
+          <t>63062</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>82714</t>
+          <t>82988</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>57,08%</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -9268,92 +9268,92 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
+          <t>4626</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>6,07%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>19,68%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>1428</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
           <t>4962</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>6,07%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>21,11%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>1428</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>4955</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4992</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13107</t>
+          <t>12750</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4359</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12075</t>
+          <t>11950</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>10998</t>
+          <t>11192</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>21941</t>
+          <t>22726</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>39,08%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>12519</t>
+          <t>12299</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>17086</t>
+          <t>16499</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>28,37%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>5279</t>
+          <t>5805</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>13293</t>
+          <t>13992</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>14003</t>
+          <t>14449</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>23551</t>
+          <t>23896</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>22282</t>
+          <t>22997</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>33924</t>
+          <t>35065</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>60,3%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2914</t>
+          <t>2909</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>11989</t>
+          <t>11966</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>609</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>4408</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>14486</t>
+          <t>14200</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>5694</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>16492</t>
+          <t>16122</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>6297</t>
+          <t>6738</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>17484</t>
+          <t>17590</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>14695</t>
+          <t>13923</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>30210</t>
+          <t>29134</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>53392</t>
+          <t>53450</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>76239</t>
+          <t>76564</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>67755</t>
+          <t>67627</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>92231</t>
+          <t>92894</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>129053</t>
+          <t>127875</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>162528</t>
+          <t>161426</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>55731</t>
+          <t>56191</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>79135</t>
+          <t>79031</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>41085</t>
+          <t>42208</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>62805</t>
+          <t>62703</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>104268</t>
+          <t>103056</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>136176</t>
+          <t>136334</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,84%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>133713</t>
+          <t>132686</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>160973</t>
+          <t>161073</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>143739</t>
+          <t>143985</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>172937</t>
+          <t>173111</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>284679</t>
+          <t>285179</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>323207</t>
+          <t>323042</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,11%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2016 (tasa de respuesta: 95,28%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a en 2016 (tasa de respuesta: 95,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10753,7 +10753,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10768,7 +10768,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10823,7 +10823,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>701</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,47 +10911,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>15,71%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>3512</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>7494</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>5,08%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>1,86%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>14,61%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>3512</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>1267</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>7081</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>5,08%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6037</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14574</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8295</t>
+          <t>8457</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9099</t>
+          <t>9775</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20645</t>
+          <t>20754</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,0%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>11738</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>5937</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15139</t>
+          <t>14855</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11878</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23855</t>
+          <t>24255</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>35,07%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8274</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17615</t>
+          <t>17387</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14938</t>
+          <t>15202</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25196</t>
+          <t>25111</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25693</t>
+          <t>26004</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39796</t>
+          <t>40414</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>58,43%</t>
         </is>
       </c>
     </row>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11485,7 +11485,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>4741</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9167</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11396</t>
+          <t>11610</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8334</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18776</t>
+          <t>19133</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>5359</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15586</t>
+          <t>14604</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17015</t>
+          <t>16479</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>30591</t>
+          <t>30341</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,47%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9551</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19855</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8462</t>
+          <t>7711</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18698</t>
+          <t>18059</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20151</t>
+          <t>20256</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34354</t>
+          <t>35460</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>36,78%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11185</t>
+          <t>11466</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22355</t>
+          <t>22424</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16898</t>
+          <t>17201</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28372</t>
+          <t>28792</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31639</t>
+          <t>31387</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47055</t>
+          <t>46798</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,54%</t>
         </is>
       </c>
     </row>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3068</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5467</t>
+          <t>5460</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12245,7 +12245,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12300,7 +12300,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5998</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4394</t>
+          <t>4366</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12168</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7366</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16744</t>
+          <t>16384</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13597</t>
+          <t>13718</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26216</t>
+          <t>26626</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>39,47%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10268</t>
+          <t>9493</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,49 +12466,49 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>34,47%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>9491</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>5506</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>14885</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>23,78%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>13,79%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
           <t>37,29%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>9491</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>5609</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>15326</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>23,78%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>14,05%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>38,4%</t>
-        </is>
-      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>22</t>
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>10679</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20837</t>
+          <t>22233</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>32,96%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7333</t>
+          <t>7573</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15811</t>
+          <t>15920</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13489</t>
+          <t>14610</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23959</t>
+          <t>24290</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24230</t>
+          <t>23225</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37136</t>
+          <t>37285</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>55,27%</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6377</t>
+          <t>6447</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>668</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9352</t>
+          <t>9162</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3266</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11006</t>
+          <t>11154</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>16925</t>
+          <t>17188</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12813</t>
+          <t>12697</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26088</t>
+          <t>26100</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14423</t>
+          <t>14513</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>28599</t>
+          <t>27967</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>31153</t>
+          <t>30240</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>50708</t>
+          <t>49699</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20336</t>
+          <t>20366</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35274</t>
+          <t>34666</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>15825</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28522</t>
+          <t>29949</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39126</t>
+          <t>39458</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>60020</t>
+          <t>59005</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>49311</t>
+          <t>49906</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>66614</t>
+          <t>67135</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>41128</t>
+          <t>41159</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58816</t>
+          <t>58018</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>95346</t>
+          <t>93946</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>119535</t>
+          <t>118522</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>56,62%</t>
         </is>
       </c>
     </row>
@@ -13481,7 +13481,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13496,7 +13496,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13516,7 +13516,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>618</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5937</t>
+          <t>5354</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9198</t>
+          <t>9492</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13629,7 +13629,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>4539</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11187</t>
+          <t>11233</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -13702,7 +13702,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7983</t>
+          <t>8153</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -13717,7 +13717,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8965</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21423</t>
+          <t>20705</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>18990</t>
+          <t>18727</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>35071</t>
+          <t>36039</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>25,23%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>14788</t>
+          <t>15438</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>27671</t>
+          <t>28080</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>24197</t>
+          <t>23379</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>37904</t>
+          <t>37881</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>41626</t>
+          <t>42096</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>60891</t>
+          <t>60237</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,17%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>26540</t>
+          <t>26226</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>40002</t>
+          <t>41064</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>16526</t>
+          <t>17044</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>31117</t>
+          <t>30129</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>47943</t>
+          <t>47066</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>67588</t>
+          <t>66063</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>46,24%</t>
         </is>
       </c>
     </row>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3621</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14233,7 +14233,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4072</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14248,7 +14248,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,47 +14321,47 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>15,2%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>3426</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>7593</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>4,86%</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
           <t>1,82%</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>15,9%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>3426</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>1291</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>7066</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>4,86%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>14786</t>
+          <t>14957</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>7525</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9026</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>20775</t>
+          <t>20589</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,2%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>11298</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>11376</t>
+          <t>11449</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>8517</t>
+          <t>9007</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>20025</t>
+          <t>20375</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>10156</t>
+          <t>10507</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>19737</t>
+          <t>19858</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>18461</t>
+          <t>18563</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>27853</t>
+          <t>28259</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>30570</t>
+          <t>31611</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>44565</t>
+          <t>44833</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,58%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1706</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>9659</t>
+          <t>9353</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>8652</t>
+          <t>8177</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>14358</t>
+          <t>13722</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>12457</t>
+          <t>12662</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>25730</t>
+          <t>26061</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>8082</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>19867</t>
+          <t>20277</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>23674</t>
+          <t>23666</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>41475</t>
+          <t>41260</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15043,7 +15043,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>61032</t>
+          <t>60901</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>85441</t>
+          <t>85807</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>53318</t>
+          <t>53025</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>76072</t>
+          <t>77612</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>119228</t>
+          <t>122367</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>154737</t>
+          <t>157026</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>70948</t>
+          <t>70128</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>95347</t>
+          <t>96504</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>78055</t>
+          <t>78224</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>106538</t>
+          <t>106143</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>156246</t>
+          <t>156492</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>192780</t>
+          <t>193197</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>131953</t>
+          <t>131277</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>160732</t>
+          <t>161404</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>144833</t>
+          <t>143223</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>174447</t>
+          <t>174156</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>283847</t>
+          <t>283171</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>328391</t>
+          <t>328333</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>50,07%</t>
         </is>
       </c>
     </row>
